--- a/outputs_xlsx_solution/test33.4-wide-NB-1.xlsx
+++ b/outputs_xlsx_solution/test33.4-wide-NB-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -927,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -947,13 +953,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -973,16 +979,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -1002,16 +1008,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1031,16 +1037,16 @@
         <v>9</v>
       </c>
       <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -1060,16 +1066,16 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
       <c r="K7" t="s">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1092,13 +1098,13 @@
         <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1118,19 +1124,19 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1141,7 +1147,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -1150,22 +1156,25 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>15</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1185,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -1194,25 +1203,25 @@
         <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -1223,7 +1232,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -1232,7 +1241,7 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -1244,10 +1253,10 @@
         <v>14</v>
       </c>
       <c r="W12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1258,7 +1267,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1267,7 +1276,13 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="X13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>15</v>
       </c>
       <c r="Z13" t="s">
         <v>14</v>
@@ -1282,7 +1297,7 @@
         <v>14</v>
       </c>
       <c r="AD13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -1293,7 +1308,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1314,28 +1329,28 @@
         <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1346,7 +1361,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1373,22 +1388,22 @@
         <v>14</v>
       </c>
       <c r="R15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1399,7 +1414,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1408,28 +1423,28 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M16" t="s">
         <v>14</v>
       </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -1449,19 +1464,19 @@
         <v>9</v>
       </c>
       <c r="L17" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" t="s">
         <v>15</v>
       </c>
-      <c r="M17" t="s">
-        <v>14</v>
-      </c>
       <c r="N17" t="s">
         <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1472,7 +1487,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
@@ -1481,16 +1496,16 @@
         <v>9</v>
       </c>
       <c r="M18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P18" t="s">
         <v>14</v>
       </c>
       <c r="Q18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1501,7 +1516,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -1510,16 +1525,16 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R19" t="s">
         <v>14</v>
       </c>
       <c r="S19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1530,7 +1545,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
@@ -1539,31 +1554,31 @@
         <v>9</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V20" t="s">
         <v>14</v>
@@ -1578,10 +1593,10 @@
         <v>14</v>
       </c>
       <c r="Z20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1592,7 +1607,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
@@ -1601,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="U21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z21" t="s">
         <v>14</v>
@@ -1613,10 +1628,10 @@
         <v>14</v>
       </c>
       <c r="AC21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1627,7 +1642,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>5</v>
@@ -1636,22 +1651,22 @@
         <v>9</v>
       </c>
       <c r="U22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC22" t="s">
         <v>14</v>
       </c>
       <c r="AD22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1662,7 +1677,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
         <v>5</v>
@@ -1671,16 +1686,16 @@
         <v>9</v>
       </c>
       <c r="U23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V23" t="s">
         <v>14</v>
       </c>
       <c r="W23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1691,7 +1706,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
         <v>5</v>
@@ -1700,16 +1715,16 @@
         <v>9</v>
       </c>
       <c r="V24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W24" t="s">
         <v>14</v>
       </c>
       <c r="X24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1720,7 +1735,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X25" t="s">
         <v>5</v>
@@ -1729,16 +1744,16 @@
         <v>9</v>
       </c>
       <c r="Z25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="s">
         <v>14</v>
       </c>
       <c r="AB25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1749,7 +1764,7 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X26" t="s">
         <v>5</v>
@@ -1758,7 +1773,13 @@
         <v>9</v>
       </c>
       <c r="Z26" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>15</v>
       </c>
       <c r="AD26" t="s">
         <v>14</v>
@@ -1773,7 +1794,7 @@
         <v>14</v>
       </c>
       <c r="AH26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1784,7 +1805,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X27" t="s">
         <v>5</v>
@@ -1793,7 +1814,7 @@
         <v>9</v>
       </c>
       <c r="Z27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AH27" t="s">
         <v>14</v>
@@ -1805,7 +1826,7 @@
         <v>14</v>
       </c>
       <c r="AK27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1816,7 +1837,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X28" t="s">
         <v>5</v>
@@ -1825,19 +1846,19 @@
         <v>9</v>
       </c>
       <c r="Z28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="s">
         <v>14</v>
       </c>
       <c r="AL28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AM28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1848,7 +1869,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y29" t="s">
         <v>5</v>
@@ -1857,25 +1878,25 @@
         <v>9</v>
       </c>
       <c r="AA29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AD29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE29" t="s">
         <v>14</v>
       </c>
       <c r="AF29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -1886,7 +1907,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y30" t="s">
         <v>5</v>
@@ -1895,16 +1916,16 @@
         <v>9</v>
       </c>
       <c r="AD30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="s">
         <v>14</v>
       </c>
       <c r="AG30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -1915,7 +1936,7 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z31" t="s">
         <v>5</v>
@@ -1927,10 +1948,10 @@
         <v>14</v>
       </c>
       <c r="AE31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1941,7 +1962,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z32" t="s">
         <v>5</v>
@@ -1950,7 +1971,16 @@
         <v>9</v>
       </c>
       <c r="AD32" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>15</v>
       </c>
       <c r="AH32" t="s">
         <v>14</v>
@@ -1965,10 +1995,10 @@
         <v>14</v>
       </c>
       <c r="AL32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -1979,7 +2009,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z33" t="s">
         <v>5</v>
@@ -1988,7 +2018,7 @@
         <v>9</v>
       </c>
       <c r="AE33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AL33" t="s">
         <v>14</v>
@@ -2000,7 +2030,7 @@
         <v>14</v>
       </c>
       <c r="AO33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -2011,7 +2041,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z34" t="s">
         <v>5</v>
@@ -2020,22 +2050,22 @@
         <v>9</v>
       </c>
       <c r="AE34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AO34" t="s">
         <v>14</v>
       </c>
       <c r="AP34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AQ34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -2046,7 +2076,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA35" t="s">
         <v>5</v>
@@ -2055,16 +2085,16 @@
         <v>9</v>
       </c>
       <c r="AG35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AH35" t="s">
         <v>14</v>
       </c>
       <c r="AI35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -2075,7 +2105,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA36" t="s">
         <v>5</v>
@@ -2084,16 +2114,16 @@
         <v>9</v>
       </c>
       <c r="AG36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI36" t="s">
         <v>14</v>
       </c>
       <c r="AJ36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
@@ -2104,7 +2134,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AJ37" t="s">
         <v>5</v>
@@ -2113,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="AL37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM37" t="s">
         <v>14</v>
@@ -2125,10 +2155,10 @@
         <v>14</v>
       </c>
       <c r="AP37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
@@ -2139,7 +2169,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AJ38" t="s">
         <v>5</v>
@@ -2148,7 +2178,7 @@
         <v>9</v>
       </c>
       <c r="AL38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AP38" t="s">
         <v>14</v>
@@ -2160,19 +2190,19 @@
         <v>14</v>
       </c>
       <c r="AS38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AU38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AV38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AW38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -2183,7 +2213,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AJ39" t="s">
         <v>5</v>
@@ -2195,10 +2225,10 @@
         <v>14</v>
       </c>
       <c r="AM39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -2209,7 +2239,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AJ40" t="s">
         <v>5</v>
@@ -2218,10 +2248,10 @@
         <v>14</v>
       </c>
       <c r="AM40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -2232,7 +2262,7 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK41" t="s">
         <v>5</v>
@@ -2241,10 +2271,10 @@
         <v>9</v>
       </c>
       <c r="AM41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO41" t="s">
         <v>14</v>
@@ -2256,22 +2286,22 @@
         <v>14</v>
       </c>
       <c r="AR41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AU41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AV41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2282,7 +2312,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK42" t="s">
         <v>5</v>
@@ -2291,10 +2321,10 @@
         <v>9</v>
       </c>
       <c r="AO42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AV42" t="s">
         <v>14</v>
@@ -2306,7 +2336,7 @@
         <v>14</v>
       </c>
       <c r="AY42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -2317,7 +2347,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK43" t="s">
         <v>5</v>
@@ -2326,7 +2356,7 @@
         <v>9</v>
       </c>
       <c r="AP43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AY43" t="s">
         <v>14</v>
@@ -2341,7 +2371,7 @@
         <v>14</v>
       </c>
       <c r="BC43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -2352,7 +2382,7 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK44" t="s">
         <v>5</v>
@@ -2373,22 +2403,22 @@
         <v>14</v>
       </c>
       <c r="AT44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AU44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AV44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AW44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AX44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -2399,7 +2429,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL45" t="s">
         <v>5</v>
@@ -2426,28 +2456,28 @@
         <v>14</v>
       </c>
       <c r="AV45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AW45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AX45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AY45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AZ45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BA45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BB45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -2458,7 +2488,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL46" t="s">
         <v>5</v>
@@ -2470,10 +2500,10 @@
         <v>14</v>
       </c>
       <c r="AR46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -2493,22 +2523,22 @@
         <v>9</v>
       </c>
       <c r="AQ47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR47" t="s">
         <v>14</v>
       </c>
       <c r="AS47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AU47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -2519,7 +2549,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL48" t="s">
         <v>5</v>
@@ -2528,16 +2558,16 @@
         <v>9</v>
       </c>
       <c r="AQ48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AR48" t="s">
         <v>14</v>
       </c>
       <c r="AS48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -2548,7 +2578,7 @@
         <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM49" t="s">
         <v>5</v>
@@ -2557,16 +2587,19 @@
         <v>9</v>
       </c>
       <c r="AQ49" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="AR49" t="s">
+        <v>15</v>
       </c>
       <c r="AS49" t="s">
         <v>14</v>
       </c>
       <c r="AT49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -2577,7 +2610,7 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM50" t="s">
         <v>5</v>
@@ -2586,26 +2619,38 @@
         <v>9</v>
       </c>
       <c r="AR50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX50" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY50" t="s">
         <v>15</v>
       </c>
-      <c r="AS50" t="s">
+      <c r="AZ50" t="s">
         <v>15</v>
       </c>
-      <c r="AT50" t="s">
+      <c r="BA50" t="s">
         <v>15</v>
       </c>
-      <c r="AU50" t="s">
+      <c r="BB50" t="s">
         <v>15</v>
       </c>
-      <c r="AV50" t="s">
-        <v>15</v>
-      </c>
-      <c r="AW50" t="s">
-        <v>15</v>
-      </c>
-      <c r="AX50" t="s">
-        <v>33</v>
-      </c>
       <c r="BC50" t="s">
         <v>14</v>
       </c>
@@ -2619,7 +2664,7 @@
         <v>14</v>
       </c>
       <c r="BG50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -2630,7 +2675,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM51" t="s">
         <v>5</v>
@@ -2639,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="AX51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BG51" t="s">
         <v>14</v>
@@ -2651,7 +2696,7 @@
         <v>14</v>
       </c>
       <c r="BJ51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -2662,7 +2707,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM52" t="s">
         <v>5</v>
@@ -2671,16 +2716,16 @@
         <v>9</v>
       </c>
       <c r="AX52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BJ52" t="s">
         <v>14</v>
       </c>
       <c r="BK52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2691,7 +2736,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AN53" t="s">
         <v>5</v>
@@ -2700,16 +2745,16 @@
         <v>9</v>
       </c>
       <c r="AX53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AY53" t="s">
         <v>14</v>
       </c>
       <c r="AZ53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -2720,7 +2765,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AN54" t="s">
         <v>5</v>
@@ -2729,16 +2774,16 @@
         <v>9</v>
       </c>
       <c r="AY54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AZ54" t="s">
         <v>14</v>
       </c>
       <c r="BA54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2749,7 +2794,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO55" t="s">
         <v>5</v>
@@ -2758,16 +2803,16 @@
         <v>9</v>
       </c>
       <c r="AY55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AZ55" t="s">
         <v>14</v>
       </c>
       <c r="BA55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -2778,7 +2823,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO56" t="s">
         <v>5</v>
@@ -2787,20 +2832,29 @@
         <v>9</v>
       </c>
       <c r="AY56" t="s">
+        <v>16</v>
+      </c>
+      <c r="AZ56" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA56" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB56" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC56" t="s">
+        <v>34</v>
+      </c>
+      <c r="BD56" t="s">
         <v>15</v>
       </c>
-      <c r="AZ56" t="s">
+      <c r="BE56" t="s">
         <v>15</v>
       </c>
-      <c r="BA56" t="s">
+      <c r="BF56" t="s">
         <v>15</v>
       </c>
-      <c r="BB56" t="s">
-        <v>15</v>
-      </c>
-      <c r="BC56" t="s">
-        <v>33</v>
-      </c>
       <c r="BG56" t="s">
         <v>14</v>
       </c>
@@ -2814,10 +2868,10 @@
         <v>14</v>
       </c>
       <c r="BK56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BM56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -2828,7 +2882,7 @@
         <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO57" t="s">
         <v>5</v>
@@ -2837,7 +2891,7 @@
         <v>9</v>
       </c>
       <c r="BC57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BK57" t="s">
         <v>14</v>
@@ -2849,10 +2903,10 @@
         <v>14</v>
       </c>
       <c r="BN57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BO57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -2863,7 +2917,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO58" t="s">
         <v>5</v>
@@ -2872,16 +2926,16 @@
         <v>9</v>
       </c>
       <c r="BC58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BO58" t="s">
         <v>14</v>
       </c>
       <c r="BP58" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BQ58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -2892,7 +2946,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AQ59" t="s">
         <v>5</v>
@@ -2901,19 +2955,19 @@
         <v>9</v>
       </c>
       <c r="BC59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BD59" t="s">
         <v>14</v>
       </c>
       <c r="BE59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BF59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -2924,7 +2978,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AQ60" t="s">
         <v>5</v>
@@ -2933,16 +2987,16 @@
         <v>9</v>
       </c>
       <c r="BD60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BF60" t="s">
         <v>14</v>
       </c>
       <c r="BG60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -2953,7 +3007,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW61" t="s">
         <v>5</v>
@@ -2965,10 +3019,10 @@
         <v>14</v>
       </c>
       <c r="BE61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -2979,7 +3033,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW62" t="s">
         <v>5</v>
@@ -2988,17 +3042,26 @@
         <v>9</v>
       </c>
       <c r="BD62" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE62" t="s">
+        <v>16</v>
+      </c>
+      <c r="BF62" t="s">
+        <v>16</v>
+      </c>
+      <c r="BG62" t="s">
+        <v>34</v>
+      </c>
+      <c r="BH62" t="s">
         <v>15</v>
       </c>
-      <c r="BE62" t="s">
+      <c r="BI62" t="s">
         <v>15</v>
       </c>
-      <c r="BF62" t="s">
+      <c r="BJ62" t="s">
         <v>15</v>
       </c>
-      <c r="BG62" t="s">
-        <v>33</v>
-      </c>
       <c r="BK62" t="s">
         <v>14</v>
       </c>
@@ -3012,13 +3075,13 @@
         <v>14</v>
       </c>
       <c r="BO62" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BP62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -3029,7 +3092,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW63" t="s">
         <v>5</v>
@@ -3038,7 +3101,7 @@
         <v>9</v>
       </c>
       <c r="BG63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BP63" t="s">
         <v>14</v>
@@ -3050,7 +3113,7 @@
         <v>14</v>
       </c>
       <c r="BS63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -3061,7 +3124,7 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW64" t="s">
         <v>5</v>
@@ -3070,31 +3133,31 @@
         <v>9</v>
       </c>
       <c r="BG64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BI64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BJ64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BK64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BL64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BS64" t="s">
         <v>14</v>
       </c>
       <c r="BT64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BU64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -3105,7 +3168,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AX65" t="s">
         <v>5</v>
@@ -3114,16 +3177,16 @@
         <v>9</v>
       </c>
       <c r="BL65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BM65" t="s">
         <v>14</v>
       </c>
       <c r="BN65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
@@ -3134,7 +3197,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AY66" t="s">
         <v>5</v>
@@ -3143,16 +3206,16 @@
         <v>9</v>
       </c>
       <c r="BL66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BN66" t="s">
         <v>14</v>
       </c>
       <c r="BO66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -3163,7 +3226,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BO67" t="s">
         <v>5</v>
@@ -3181,10 +3244,10 @@
         <v>14</v>
       </c>
       <c r="BT67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -3195,7 +3258,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BO68" t="s">
         <v>5</v>
@@ -3204,7 +3267,7 @@
         <v>9</v>
       </c>
       <c r="BQ68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BT68" t="s">
         <v>14</v>
@@ -3216,16 +3279,16 @@
         <v>14</v>
       </c>
       <c r="BW68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BX68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BY68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BZ68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -3236,7 +3299,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BO69" t="s">
         <v>5</v>
@@ -3248,10 +3311,10 @@
         <v>14</v>
       </c>
       <c r="BR69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BZ69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -3262,7 +3325,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BO70" t="s">
         <v>5</v>
@@ -3274,10 +3337,10 @@
         <v>14</v>
       </c>
       <c r="BR70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BZ70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -3288,7 +3351,7 @@
         <v>36</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BP71" t="s">
         <v>5</v>
@@ -3297,7 +3360,7 @@
         <v>9</v>
       </c>
       <c r="BR71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BS71" t="s">
         <v>14</v>
@@ -3309,22 +3372,22 @@
         <v>14</v>
       </c>
       <c r="BV71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BW71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BX71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BY71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BZ71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -3335,7 +3398,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BP72" t="s">
         <v>5</v>
@@ -3344,10 +3407,10 @@
         <v>9</v>
       </c>
       <c r="BS72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BT72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CA72" t="s">
         <v>14</v>
@@ -3359,13 +3422,13 @@
         <v>14</v>
       </c>
       <c r="CD72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CE72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CF72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -3376,7 +3439,7 @@
         <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BP73" t="s">
         <v>5</v>
@@ -3385,7 +3448,10 @@
         <v>9</v>
       </c>
       <c r="BT73" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="CF73" t="s">
+        <v>15</v>
       </c>
       <c r="CG73" t="s">
         <v>14</v>
@@ -3400,7 +3466,7 @@
         <v>14</v>
       </c>
       <c r="CK73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -3411,7 +3477,7 @@
         <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BP74" t="s">
         <v>5</v>
@@ -3432,22 +3498,22 @@
         <v>14</v>
       </c>
       <c r="BX74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BY74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BZ74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -3458,7 +3524,7 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ75" t="s">
         <v>5</v>
@@ -3485,19 +3551,19 @@
         <v>14</v>
       </c>
       <c r="BZ75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
@@ -3508,7 +3574,7 @@
         <v>56</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ76" t="s">
         <v>5</v>
@@ -3520,10 +3586,10 @@
         <v>14</v>
       </c>
       <c r="BV76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3543,22 +3609,22 @@
         <v>9</v>
       </c>
       <c r="BU77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BV77" t="s">
         <v>14</v>
       </c>
       <c r="BW77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BX77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BY77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -3569,7 +3635,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ78" t="s">
         <v>5</v>
@@ -3578,16 +3644,16 @@
         <v>9</v>
       </c>
       <c r="BU78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BV78" t="s">
         <v>14</v>
       </c>
       <c r="BW78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3664,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BR79" t="s">
         <v>5</v>
@@ -3607,16 +3673,19 @@
         <v>9</v>
       </c>
       <c r="BU79" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="BV79" t="s">
+        <v>15</v>
       </c>
       <c r="BW79" t="s">
         <v>14</v>
       </c>
       <c r="BX79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -3627,7 +3696,7 @@
         <v>72</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BR80" t="s">
         <v>5</v>
@@ -3636,25 +3705,25 @@
         <v>9</v>
       </c>
       <c r="BV80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BX80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BY80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BZ80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CA80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CB80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CC80" t="s">
         <v>14</v>
@@ -3669,10 +3738,10 @@
         <v>14</v>
       </c>
       <c r="CG80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -3683,7 +3752,7 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BR81" t="s">
         <v>5</v>
@@ -3692,7 +3761,7 @@
         <v>9</v>
       </c>
       <c r="CB81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CG81" t="s">
         <v>14</v>
@@ -3704,10 +3773,10 @@
         <v>14</v>
       </c>
       <c r="CJ81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CM81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3787,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BR82" t="s">
         <v>5</v>
@@ -3727,22 +3796,22 @@
         <v>9</v>
       </c>
       <c r="CB82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CJ82" t="s">
         <v>14</v>
       </c>
       <c r="CK82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CL82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CM82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CN82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -3753,7 +3822,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BS83" t="s">
         <v>5</v>
@@ -3762,16 +3831,16 @@
         <v>9</v>
       </c>
       <c r="CB83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CC83" t="s">
         <v>14</v>
       </c>
       <c r="CD83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CN83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -3782,7 +3851,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BS84" t="s">
         <v>5</v>
@@ -3791,16 +3860,16 @@
         <v>9</v>
       </c>
       <c r="CC84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CD84" t="s">
         <v>14</v>
       </c>
       <c r="CE84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CN84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -3811,7 +3880,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BT85" t="s">
         <v>5</v>
@@ -3820,16 +3889,16 @@
         <v>9</v>
       </c>
       <c r="CC85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CD85" t="s">
         <v>14</v>
       </c>
       <c r="CE85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CN85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -3840,7 +3909,7 @@
         <v>72</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BT86" t="s">
         <v>5</v>
@@ -3849,20 +3918,29 @@
         <v>9</v>
       </c>
       <c r="CC86" t="s">
+        <v>16</v>
+      </c>
+      <c r="CD86" t="s">
+        <v>16</v>
+      </c>
+      <c r="CE86" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF86" t="s">
+        <v>16</v>
+      </c>
+      <c r="CG86" t="s">
+        <v>34</v>
+      </c>
+      <c r="CH86" t="s">
         <v>15</v>
       </c>
-      <c r="CD86" t="s">
+      <c r="CI86" t="s">
         <v>15</v>
       </c>
-      <c r="CE86" t="s">
+      <c r="CJ86" t="s">
         <v>15</v>
       </c>
-      <c r="CF86" t="s">
-        <v>15</v>
-      </c>
-      <c r="CG86" t="s">
-        <v>33</v>
-      </c>
       <c r="CK86" t="s">
         <v>14</v>
       </c>
@@ -3876,7 +3954,7 @@
         <v>14</v>
       </c>
       <c r="CO86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -3887,7 +3965,7 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BT87" t="s">
         <v>5</v>
@@ -3896,7 +3974,7 @@
         <v>9</v>
       </c>
       <c r="CG87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CO87" t="s">
         <v>14</v>
@@ -3908,7 +3986,7 @@
         <v>14</v>
       </c>
       <c r="CR87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
@@ -3919,7 +3997,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BT88" t="s">
         <v>5</v>
@@ -3928,19 +4006,19 @@
         <v>9</v>
       </c>
       <c r="CG88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CR88" t="s">
         <v>14</v>
       </c>
       <c r="CS88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CT88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CU88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
@@ -3951,7 +4029,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BU89" t="s">
         <v>5</v>
@@ -3960,28 +4038,28 @@
         <v>9</v>
       </c>
       <c r="CG89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CH89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CI89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CJ89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CK89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CL89" t="s">
         <v>14</v>
       </c>
       <c r="CM89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CU89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -3992,7 +4070,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BU90" t="s">
         <v>5</v>
@@ -4001,16 +4079,16 @@
         <v>9</v>
       </c>
       <c r="CK90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CM90" t="s">
         <v>14</v>
       </c>
       <c r="CN90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CU90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -4021,7 +4099,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BZ91" t="s">
         <v>5</v>
@@ -4033,10 +4111,10 @@
         <v>14</v>
       </c>
       <c r="CL91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CU91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -4047,7 +4125,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BZ92" t="s">
         <v>5</v>
@@ -4056,7 +4134,16 @@
         <v>9</v>
       </c>
       <c r="CK92" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="CL92" t="s">
+        <v>15</v>
+      </c>
+      <c r="CM92" t="s">
+        <v>15</v>
+      </c>
+      <c r="CN92" t="s">
+        <v>15</v>
       </c>
       <c r="CO92" t="s">
         <v>14</v>
@@ -4071,10 +4158,10 @@
         <v>14</v>
       </c>
       <c r="CS92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CV92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -4085,7 +4172,7 @@
         <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BZ93" t="s">
         <v>5</v>
@@ -4094,7 +4181,7 @@
         <v>9</v>
       </c>
       <c r="CL93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CS93" t="s">
         <v>14</v>
@@ -4106,7 +4193,7 @@
         <v>14</v>
       </c>
       <c r="CV93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -4117,7 +4204,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BZ94" t="s">
         <v>5</v>
@@ -4126,22 +4213,22 @@
         <v>9</v>
       </c>
       <c r="CL94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CM94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CN94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CV94" t="s">
         <v>14</v>
       </c>
       <c r="CW94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CX94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -4152,7 +4239,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CA95" t="s">
         <v>5</v>
@@ -4161,16 +4248,16 @@
         <v>9</v>
       </c>
       <c r="CN95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CO95" t="s">
         <v>14</v>
       </c>
       <c r="CP95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CX95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -4181,7 +4268,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CF96" t="s">
         <v>5</v>
@@ -4190,16 +4277,16 @@
         <v>9</v>
       </c>
       <c r="CN96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CP96" t="s">
         <v>14</v>
       </c>
       <c r="CQ96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CX96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -4210,7 +4297,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CQ97" t="s">
         <v>5</v>
@@ -4219,7 +4306,7 @@
         <v>9</v>
       </c>
       <c r="CS97" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CT97" t="s">
         <v>14</v>
@@ -4231,10 +4318,10 @@
         <v>14</v>
       </c>
       <c r="CW97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CX97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -4245,7 +4332,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CQ98" t="s">
         <v>5</v>
@@ -4254,7 +4341,7 @@
         <v>9</v>
       </c>
       <c r="CS98" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CW98" t="s">
         <v>14</v>
@@ -4266,7 +4353,7 @@
         <v>14</v>
       </c>
       <c r="CZ98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -4277,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CQ99" t="s">
         <v>5</v>
@@ -4289,10 +4376,10 @@
         <v>14</v>
       </c>
       <c r="CT99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CZ99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -4303,7 +4390,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CQ100" t="s">
         <v>5</v>
@@ -4312,10 +4399,10 @@
         <v>14</v>
       </c>
       <c r="CT100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CZ100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
@@ -4326,7 +4413,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CR101" t="s">
         <v>5</v>
@@ -4335,49 +4422,49 @@
         <v>9</v>
       </c>
       <c r="CT101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CU101" t="s">
         <v>14</v>
       </c>
       <c r="CV101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CW101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CX101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CY101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CZ101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DA101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DB101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DC101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DD101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DE101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DF101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DG101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DH101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -4388,7 +4475,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CR102" t="s">
         <v>5</v>
@@ -4397,22 +4484,22 @@
         <v>9</v>
       </c>
       <c r="CU102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CX102" t="s">
         <v>14</v>
       </c>
       <c r="CY102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DH102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -4423,7 +4510,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CR103" t="s">
         <v>5</v>
@@ -4432,19 +4519,19 @@
         <v>9</v>
       </c>
       <c r="CX103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CY103" t="s">
         <v>14</v>
       </c>
       <c r="CZ103" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DA103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DH103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -4455,7 +4542,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CR104" t="s">
         <v>5</v>
@@ -4464,19 +4551,19 @@
         <v>9</v>
       </c>
       <c r="CY104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CZ104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DA104" t="s">
         <v>14</v>
       </c>
       <c r="DB104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DH104" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
@@ -4487,7 +4574,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CS105" t="s">
         <v>5</v>
@@ -4496,16 +4583,16 @@
         <v>9</v>
       </c>
       <c r="DA105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DB105" t="s">
         <v>14</v>
       </c>
       <c r="DC105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DI105" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
@@ -4516,7 +4603,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CS106" t="s">
         <v>5</v>
@@ -4525,16 +4612,16 @@
         <v>9</v>
       </c>
       <c r="DB106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DC106" t="s">
         <v>14</v>
       </c>
       <c r="DD106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DI106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -4545,7 +4632,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CS107" t="s">
         <v>5</v>
@@ -4554,16 +4641,16 @@
         <v>9</v>
       </c>
       <c r="DC107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DD107" t="s">
         <v>14</v>
       </c>
       <c r="DE107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DI107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
@@ -4574,7 +4661,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CS108" t="s">
         <v>5</v>
@@ -4583,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="DD108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DE108" t="s">
         <v>14</v>
       </c>
       <c r="DF108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DI108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -4603,7 +4690,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="CT109" t="s">
         <v>5</v>
@@ -4612,21 +4699,21 @@
         <v>9</v>
       </c>
       <c r="DE109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DF109" t="s">
         <v>14</v>
       </c>
       <c r="DG109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DJ109" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112">
@@ -4634,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
@@ -4642,15 +4729,15 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="115">
@@ -4658,39 +4745,55 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B119" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
